--- a/Research Logs/Matt/Matt Baker - Week 13 Research Log.xlsx
+++ b/Research Logs/Matt/Matt Baker - Week 13 Research Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RecoveryAdmin\Documents\BHB-Capstone\Research Logs\Matt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB419E9-0FA4-45EC-A081-A992DB4E3F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92B2DA5-25C2-4BD3-BFD1-A593F7FEC3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2910" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16875" yWindow="1020" windowWidth="14655" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
